--- a/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
+++ b/docs/Logic Requirements/Ageipelago Prithviraj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4368DE-7ABB-4AA6-8B11-F006EDFE1DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A202FBF-13A6-4595-9F9D-5503157ED716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="226">
   <si>
     <t>Scenario</t>
   </si>
@@ -3607,29 +3607,66 @@
     <t>Imperial Age is researched automatically on Standard</t>
   </si>
   <si>
-    <t>Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw, Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow, Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining, Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining, Kshatriyas and Frontier Guards researched when specific/enough Rajas are converted
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF2FE2F5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Capped Ram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Not on Standard)</t>
+    </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Husbandry, Light Cavalry, Chain Barding Armor, Bow Saw, Fervor, Sanctity, Long Swordsman, Arson, Chain Mail Armor, Heavy Plow, Thumb Ring, Bodkin Arrow, Leather Archer Armor, Stone Shaft Mining, Ballistics, Murder Holes, Guard Tower, Gold Shaft Mining,  researched when specific Rajas are converted FIRST
+Kshatriyas and Frontier Guards researched when enough Rajas are converted
 No Spies</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF2FE2F5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Capped Ram</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Not on Standard)</t>
-    </r>
+    <t>Prithviraj</t>
+  </si>
+  <si>
+    <t>Chand Bardai</t>
+  </si>
+  <si>
+    <t>Urumi Swordsman</t>
+  </si>
+  <si>
+    <t>Siege Onager</t>
+  </si>
+  <si>
+    <t>Sanyogita</t>
+  </si>
+  <si>
+    <t>Relic Cart</t>
+  </si>
+  <si>
+    <t>Govind Tai</t>
+  </si>
+  <si>
+    <t>Poet</t>
   </si>
 </sst>
 </file>
@@ -3814,7 +3851,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3948,11 +3985,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4002,9 +4070,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4050,24 +4115,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4096,6 +4143,46 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4722,6 +4809,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -4731,11 +4819,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -4750,18 +4838,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="23" t="s">
         <v>133</v>
       </c>
       <c r="L3" s="9" t="s">
@@ -4784,7 +4872,7 @@
       <c r="H4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>134</v>
       </c>
       <c r="L4" s="9" t="s">
@@ -4807,7 +4895,7 @@
       <c r="H5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>83</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -4824,14 +4912,14 @@
       <c r="H6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>97</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
@@ -4841,24 +4929,33 @@
       <c r="H7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>93</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>110</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -4866,16 +4963,23 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>96</v>
+      </c>
       <c r="G9" s="13" t="s">
         <v>114</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>99</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -4883,16 +4987,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>104</v>
+      </c>
       <c r="G10" s="13" t="s">
         <v>115</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="23" t="s">
         <v>135</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -4900,16 +5011,21 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50" t="s">
+        <v>98</v>
+      </c>
       <c r="G11" s="13" t="s">
         <v>116</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>136</v>
       </c>
       <c r="L11" s="9" t="s">
@@ -4917,16 +5033,21 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="48" t="s">
+        <v>95</v>
+      </c>
       <c r="G12" s="13" t="s">
         <v>88</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>98</v>
       </c>
       <c r="L12" s="9" t="s">
@@ -4934,15 +5055,21 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="B13" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="48" t="s">
+        <v>109</v>
+      </c>
       <c r="G13" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="23" t="s">
         <v>106</v>
       </c>
       <c r="L13" s="9" t="s">
@@ -4950,15 +5077,19 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="48" t="s">
+        <v>100</v>
+      </c>
       <c r="G14" s="13" t="s">
         <v>121</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="23" t="s">
         <v>109</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -4966,15 +5097,19 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="48" t="s">
+        <v>90</v>
+      </c>
       <c r="G15" s="13" t="s">
         <v>123</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="23" t="s">
         <v>100</v>
       </c>
       <c r="L15" s="9" t="s">
@@ -4982,150 +5117,196 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="G16" s="40" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="33" t="s">
         <v>124</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="18" t="s">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="17" t="s">
         <v>125</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="23" t="s">
         <v>137</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="42" t="s">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="35" t="s">
         <v>126</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="17" t="s">
         <v>102</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="18" t="s">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="17" t="s">
         <v>94</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="17" t="s">
         <v>95</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="18" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="17" t="s">
         <v>128</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="17" t="s">
         <v>103</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="18" t="s">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>111</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="17" t="s">
         <v>90</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="18" t="s">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="G22" s="17" t="s">
         <v>91</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="19" t="s">
         <v>108</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="24" t="s">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="G23" s="23" t="s">
         <v>130</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K23" s="25" t="s">
+      <c r="K23" s="24" t="s">
         <v>138</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="25" t="s">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="G24" s="24" t="s">
         <v>131</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K24" s="25" t="s">
+      <c r="K24" s="24" t="s">
         <v>139</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="26" t="s">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="K25" s="28" t="s">
+      <c r="H25" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L25" s="21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
+      <c r="L25" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
       <c r="K26" s="13" t="s">
         <v>142</v>
       </c>
@@ -5133,31 +5314,31 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="K31" s="16"/>
@@ -5179,6 +5360,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -5188,11 +5370,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5207,18 +5389,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="18" t="s">
         <v>138</v>
       </c>
       <c r="L3" s="9" t="s">
@@ -5241,7 +5423,7 @@
       <c r="H4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="18" t="s">
         <v>139</v>
       </c>
       <c r="L4" s="9" t="s">
@@ -5264,7 +5446,7 @@
       <c r="H5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>136</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -5281,14 +5463,14 @@
       <c r="H6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="18" t="s">
         <v>90</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
@@ -5298,41 +5480,59 @@
       <c r="H7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="K7" s="37" t="s">
         <v>153</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="9" t="s">
         <v>145</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="19" t="s">
         <v>99</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+    <row r="9" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="G9" s="9" t="s">
         <v>146</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="19" t="s">
         <v>93</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -5340,16 +5540,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="49"/>
       <c r="G10" s="9" t="s">
         <v>118</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="19" t="s">
         <v>97</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -5357,16 +5564,21 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="G11" s="9" t="s">
         <v>119</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="19" t="s">
         <v>98</v>
       </c>
       <c r="L11" s="9" t="s">
@@ -5374,16 +5586,21 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="G12" s="19" t="s">
+      <c r="B12" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="G12" s="18" t="s">
         <v>121</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="19" t="s">
         <v>135</v>
       </c>
       <c r="L12" s="9" t="s">
@@ -5391,16 +5608,19 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="G13" s="19" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="G13" s="18" t="s">
         <v>132</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="23" t="s">
         <v>110</v>
       </c>
       <c r="L13" s="9" t="s">
@@ -5408,16 +5628,17 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
-      <c r="G14" s="19" t="s">
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="G14" s="18" t="s">
         <v>120</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="24" t="s">
         <v>133</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -5425,16 +5646,17 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="G15" s="19" t="s">
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="G15" s="18" t="s">
         <v>115</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="24" t="s">
         <v>134</v>
       </c>
       <c r="L15" s="9" t="s">
@@ -5442,66 +5664,83 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="G16" s="19" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="G16" s="18" t="s">
         <v>113</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="25" t="s">
+      <c r="K16" s="24" t="s">
         <v>154</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="19" t="s">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="G17" s="18" t="s">
         <v>107</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="25" t="s">
+      <c r="K17" s="24" t="s">
         <v>102</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="19" t="s">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="G18" s="18" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="25" t="s">
+      <c r="K18" s="24" t="s">
         <v>105</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="19" t="s">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="G19" s="18" t="s">
         <v>147</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K19" s="25" t="s">
+      <c r="K19" s="24" t="s">
         <v>104</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="19" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="G20" s="18" t="s">
         <v>148</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -5514,8 +5753,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="20" t="s">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="G21" s="19" t="s">
         <v>88</v>
       </c>
       <c r="H21" s="9" t="s">
@@ -5528,8 +5771,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="20" t="s">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="G22" s="19" t="s">
         <v>149</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -5542,8 +5789,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="45" t="s">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="G23" s="38" t="s">
         <v>127</v>
       </c>
       <c r="H23" s="9" t="s">
@@ -5556,8 +5807,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="20" t="s">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="G24" s="19" t="s">
         <v>128</v>
       </c>
       <c r="H24" s="9" t="s">
@@ -5570,8 +5825,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="20" t="s">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="19" t="s">
         <v>111</v>
       </c>
       <c r="H25" s="9" t="s">
@@ -5584,78 +5839,78 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="45" t="s">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="38" t="s">
         <v>150</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K26" s="42" t="s">
+      <c r="K26" s="35" t="s">
         <v>155</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="45" t="s">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="38" t="s">
         <v>151</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K27" s="42" t="s">
+      <c r="K27" s="35" t="s">
         <v>156</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24" t="s">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="23" t="s">
         <v>131</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K28" s="42" t="s">
+      <c r="K28" s="35" t="s">
         <v>87</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24" t="s">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="23" t="s">
         <v>112</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K29" s="42" t="s">
+      <c r="K29" s="35" t="s">
         <v>89</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="43" t="s">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="36" t="s">
         <v>152</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K30" s="18" t="s">
+      <c r="K30" s="17" t="s">
         <v>157</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="25" t="s">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24" t="s">
         <v>125</v>
       </c>
       <c r="H31" s="9" t="s">
@@ -5664,8 +5919,8 @@
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="25" t="s">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24" t="s">
         <v>130</v>
       </c>
       <c r="H32" s="9" t="s">
@@ -5673,7 +5928,7 @@
       </c>
     </row>
     <row r="33" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="24" t="s">
         <v>94</v>
       </c>
       <c r="H33" s="9" t="s">
@@ -5681,7 +5936,7 @@
       </c>
     </row>
     <row r="34" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="25" t="s">
+      <c r="G34" s="24" t="s">
         <v>91</v>
       </c>
       <c r="H34" s="9" t="s">
@@ -5705,7 +5960,7 @@
       </c>
     </row>
     <row r="37" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="17" t="s">
         <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
@@ -5728,6 +5983,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -5737,11 +5993,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -5756,11 +6012,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="9" t="s">
         <v>77</v>
       </c>
@@ -5837,7 +6093,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
@@ -5854,10 +6110,19 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="13" t="s">
         <v>114</v>
       </c>
@@ -5872,16 +6137,25 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>95</v>
+      </c>
       <c r="G9" s="13" t="s">
         <v>107</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="18" t="s">
         <v>100</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -5889,16 +6163,23 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="G10" s="40" t="s">
+      <c r="B10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="33" t="s">
         <v>159</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="37" t="s">
         <v>169</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -5906,16 +6187,23 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>100</v>
+      </c>
       <c r="G11" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>98</v>
       </c>
       <c r="L11" s="9" t="s">
@@ -5923,16 +6211,21 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="G12" s="40" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="33" t="s">
         <v>160</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="34" t="s">
         <v>170</v>
       </c>
       <c r="L12" s="9" t="s">
@@ -5940,16 +6233,21 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>96</v>
+      </c>
       <c r="G13" s="13" t="s">
         <v>94</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="17" t="s">
         <v>108</v>
       </c>
       <c r="L13" s="9" t="s">
@@ -5957,16 +6255,19 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="49"/>
       <c r="G14" s="13" t="s">
         <v>161</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="17" t="s">
         <v>102</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -5974,16 +6275,19 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="54"/>
       <c r="G15" s="13" t="s">
         <v>101</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K15" s="42" t="s">
+      <c r="K15" s="35" t="s">
         <v>171</v>
       </c>
       <c r="L15" s="9" t="s">
@@ -5991,137 +6295,186 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="G16" s="19" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="54"/>
+      <c r="G16" s="18" t="s">
         <v>132</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="17" t="s">
         <v>83</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="44" t="s">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="54"/>
+      <c r="G17" s="37" t="s">
         <v>163</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="35" t="s">
         <v>172</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="24" t="s">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="54"/>
+      <c r="G18" s="23" t="s">
         <v>125</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="17" t="s">
         <v>104</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="24" t="s">
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="49"/>
+      <c r="G19" s="23" t="s">
         <v>149</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="17" t="s">
         <v>93</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="18" t="s">
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" s="49"/>
+      <c r="G20" s="17" t="s">
         <v>128</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K20" s="24" t="s">
+      <c r="K20" s="23" t="s">
         <v>110</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="18" t="s">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" s="49"/>
+      <c r="G21" s="17" t="s">
         <v>148</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K21" s="24" t="s">
+      <c r="K21" s="23" t="s">
         <v>134</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="42" t="s">
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="49"/>
+      <c r="G22" s="35" t="s">
         <v>175</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="K22" s="17" t="s">
         <v>157</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="42" t="s">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="49"/>
+      <c r="G23" s="35" t="s">
         <v>167</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="19" t="s">
         <v>79</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="18" t="s">
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="G24" s="17" t="s">
         <v>88</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="19" t="s">
         <v>106</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
       <c r="K25" s="13" t="s">
         <v>173</v>
       </c>
@@ -6129,9 +6482,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
       <c r="K26" s="13" t="s">
         <v>174</v>
       </c>
@@ -6139,67 +6492,67 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="K27" s="18" t="s">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="K27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="K28" s="18" t="s">
+    <row r="28" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="K28" s="17" t="s">
         <v>90</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="K29" s="18" t="s">
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="K29" s="17" t="s">
         <v>100</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="30" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="K30" s="22" t="s">
+    <row r="30" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="K30" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="L30" s="21" t="s">
+      <c r="L30" s="20" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-    </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+    </row>
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
     </row>
     <row r="33" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
     </row>
     <row r="34" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
     </row>
     <row r="35" spans="11:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6217,6 +6570,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6226,11 +6580,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6245,11 +6599,11 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="G3" s="9" t="s">
         <v>143</v>
       </c>
@@ -6326,7 +6680,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
@@ -6343,10 +6697,19 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G8" s="9" t="s">
         <v>146</v>
       </c>
@@ -6361,9 +6724,16 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" s="49"/>
       <c r="G9" s="9" t="s">
         <v>86</v>
       </c>
@@ -6378,9 +6748,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E10" s="49"/>
       <c r="G10" s="9" t="s">
         <v>145</v>
       </c>
@@ -6395,10 +6772,17 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
-      <c r="G11" s="39" t="s">
+      <c r="B11" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="49"/>
+      <c r="G11" s="32" t="s">
         <v>178</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -6412,9 +6796,14 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="13" t="s">
         <v>131</v>
       </c>
@@ -6429,9 +6818,14 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
+      <c r="B13" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="G13" s="13" t="s">
         <v>115</v>
       </c>
@@ -6446,9 +6840,14 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="G14" s="13" t="s">
         <v>94</v>
       </c>
@@ -6463,10 +6862,15 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="G15" s="40" t="s">
+      <c r="B15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="G15" s="33" t="s">
         <v>179</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -6480,9 +6884,14 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
+      <c r="B16" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="G16" s="13" t="s">
         <v>88</v>
       </c>
@@ -6496,7 +6905,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="G17" s="13" t="s">
         <v>92</v>
       </c>
@@ -6510,7 +6925,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="G18" s="13" t="s">
         <v>116</v>
       </c>
@@ -6524,142 +6945,174 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="G19" s="13" t="s">
         <v>180</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="17" t="s">
         <v>138</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="40" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="G20" s="33" t="s">
         <v>181</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="17" t="s">
         <v>139</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="G21" s="13" t="s">
         <v>182</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="17" t="s">
         <v>108</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="42" t="s">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="G22" s="35" t="s">
         <v>183</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="K22" s="18" t="s">
         <v>83</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="42" t="s">
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="G23" s="35" t="s">
         <v>184</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" s="18" t="s">
         <v>85</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="42" t="s">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="G24" s="35" t="s">
         <v>187</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="L24" s="21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="42" t="s">
+      <c r="L24" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="35" t="s">
         <v>188</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="42" t="s">
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="35" t="s">
         <v>189</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="18" t="s">
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="17" t="s">
         <v>107</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="18" t="s">
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="17" t="s">
         <v>101</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="41" t="s">
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="34" t="s">
         <v>190</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="41" t="s">
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="34" t="s">
         <v>191</v>
       </c>
       <c r="H30" s="9" t="s">
@@ -6668,8 +7121,8 @@
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24" t="s">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="23" t="s">
         <v>192</v>
       </c>
       <c r="H31" s="9" t="s">
@@ -6678,8 +7131,8 @@
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24" t="s">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="23" t="s">
         <v>193</v>
       </c>
       <c r="H32" s="9" t="s">
@@ -6687,28 +7140,28 @@
       </c>
     </row>
     <row r="33" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="46" t="s">
+      <c r="G33" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H33" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="34" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
     </row>
     <row r="35" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="7:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6726,6 +7179,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
@@ -6735,11 +7189,11 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="G2" s="2" t="s">
         <v>74</v>
       </c>
@@ -6754,18 +7208,18 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38"/>
-      <c r="G3" s="30" t="s">
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="G3" s="29" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="17" t="s">
         <v>79</v>
       </c>
       <c r="L3" s="9" t="s">
@@ -6782,13 +7236,13 @@
       <c r="D4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="29" t="s">
         <v>117</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>154</v>
       </c>
       <c r="L4" s="9" t="s">
@@ -6803,15 +7257,15 @@
         <v>209</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="G5" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="29" t="s">
         <v>144</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="35" t="s">
         <v>207</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -6822,47 +7276,56 @@
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="16"/>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="29" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="17" t="s">
         <v>110</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16"/>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="29" t="s">
         <v>146</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="17" t="s">
         <v>97</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16"/>
-      <c r="G8" s="42" t="s">
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>196</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="17" t="s">
         <v>93</v>
       </c>
       <c r="L8" s="9" t="s">
@@ -6870,16 +7333,23 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="G9" s="18" t="s">
+      <c r="B9" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>115</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="17" t="s">
         <v>135</v>
       </c>
       <c r="L9" s="9" t="s">
@@ -6887,16 +7357,21 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="G10" s="18" t="s">
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>88</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="17" t="s">
         <v>99</v>
       </c>
       <c r="L10" s="9" t="s">
@@ -6904,16 +7379,21 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="16"/>
-      <c r="G11" s="42" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="35" t="s">
         <v>198</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="17" t="s">
         <v>108</v>
       </c>
       <c r="L11" s="9" t="s">
@@ -6921,16 +7401,21 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="G12" s="18" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>132</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="17" t="s">
         <v>103</v>
       </c>
       <c r="L12" s="9" t="s">
@@ -6938,16 +7423,22 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="G13" s="18" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="55"/>
+      <c r="G13" s="17" t="s">
         <v>180</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="17" t="s">
         <v>98</v>
       </c>
       <c r="L13" s="9" t="s">
@@ -6955,16 +7446,21 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="16"/>
-      <c r="G14" s="24" t="s">
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>149</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="17" t="s">
         <v>106</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -6972,16 +7468,21 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="G15" s="41" t="s">
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="34" t="s">
         <v>199</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="17" t="s">
         <v>102</v>
       </c>
       <c r="L15" s="9" t="s">
@@ -6989,327 +7490,408 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="G16" s="41" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="34" t="s">
         <v>200</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="17" t="s">
         <v>95</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="41" t="s">
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="34" t="s">
         <v>201</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="17" t="s">
         <v>109</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="24" t="s">
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="23" t="s">
         <v>193</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="17" t="s">
         <v>100</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="41" t="s">
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="34" t="s">
         <v>202</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K19" s="18" t="s">
+      <c r="K19" s="17" t="s">
         <v>96</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="24" t="s">
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="23" t="s">
         <v>111</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="17" t="s">
         <v>173</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="43" t="s">
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="36" t="s">
         <v>203</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="18" t="s">
+      <c r="K21" s="17" t="s">
         <v>174</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="25" t="s">
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="24" t="s">
         <v>112</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K22" s="24" t="s">
+      <c r="K22" s="23" t="s">
         <v>136</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="48" t="s">
+        <v>110</v>
+      </c>
       <c r="G23" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="K23" s="23" t="s">
         <v>90</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="43" t="s">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="36" t="s">
         <v>204</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K24" s="24" t="s">
+      <c r="K24" s="23" t="s">
         <v>133</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="25" t="s">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E25" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>192</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K25" s="24" t="s">
+      <c r="K25" s="23" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G26" s="43" t="s">
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E26" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="36" t="s">
         <v>205</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K26" s="24" t="s">
+      <c r="K26" s="23" t="s">
         <v>104</v>
       </c>
       <c r="L26" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E27" s="48" t="s">
+        <v>108</v>
+      </c>
       <c r="G27" s="13" t="s">
         <v>120</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K27" s="25" t="s">
+      <c r="K27" s="24" t="s">
         <v>140</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E28" s="48" t="s">
+        <v>93</v>
+      </c>
       <c r="G28" s="13" t="s">
         <v>91</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K28" s="25" t="s">
+      <c r="K28" s="24" t="s">
         <v>83</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E29" s="48" t="s">
+        <v>110</v>
+      </c>
       <c r="G29" s="13" t="s">
         <v>121</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K29" s="25" t="s">
+      <c r="K29" s="24" t="s">
         <v>85</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E30" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="G30" s="13" t="s">
         <v>113</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K30" s="25" t="s">
+      <c r="K30" s="24" t="s">
         <v>105</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="13" t="s">
         <v>92</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="K31" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="L31" s="21" t="s">
+      <c r="L31" s="20" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="13" t="s">
         <v>116</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K32" s="31" t="s">
+      <c r="K32" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="L32" s="21" t="s">
+      <c r="L32" s="20" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="30" t="s">
         <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K33" s="48" t="s">
+      <c r="K33" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="L33" s="21" t="s">
+      <c r="L33" s="20" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G34" s="47" t="s">
+      <c r="G34" s="40" t="s">
         <v>206</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
     <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="30" t="s">
         <v>161</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
     </row>
     <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="30" t="s">
         <v>182</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
